--- a/data/trans_orig/P33B_R5-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P33B_R5-Edad-trans_orig.xlsx
@@ -725,7 +725,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>7755</t>
+          <t>6898</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -735,12 +735,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26864</t>
+          <t>25337</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>11133</t>
+          <t>11849</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3997</t>
+          <t>4363</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24191</t>
+          <t>23922</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>18888</t>
+          <t>18747</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8385</t>
+          <t>8854</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>36900</t>
+          <t>37491</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>4,87%</t>
         </is>
       </c>
     </row>
@@ -838,27 +838,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>392232</t>
+          <t>400895</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>373123</t>
+          <t>382456</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>302067</t>
+          <t>350663</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>289009</t>
+          <t>338590</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>309203</t>
+          <t>358149</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>694299</t>
+          <t>751558</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>676287</t>
+          <t>732814</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>704802</t>
+          <t>761451</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,85%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3477</t>
+          <t>5440</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1080</t>
+          <t>1228</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9499</t>
+          <t>13011</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>12962</t>
+          <t>15382</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6318</t>
+          <t>8607</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22143</t>
+          <t>24655</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>16439</t>
+          <t>20821</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9868</t>
+          <t>12512</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>27787</t>
+          <t>33076</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>420070</t>
+          <t>471450</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>414048</t>
+          <t>463879</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>422467</t>
+          <t>475662</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,74%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>498542</t>
+          <t>485701</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>489361</t>
+          <t>476428</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>505186</t>
+          <t>492476</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>918612</t>
+          <t>957152</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>907264</t>
+          <t>944897</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>925183</t>
+          <t>965461</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,72%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>20329</t>
+          <t>21761</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11827</t>
+          <t>14067</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30658</t>
+          <t>33450</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>33663</t>
+          <t>39615</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>25189</t>
+          <t>29999</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>44322</t>
+          <t>50482</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>53992</t>
+          <t>61376</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>41744</t>
+          <t>48535</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>67160</t>
+          <t>77611</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,24%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>516009</t>
+          <t>599076</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>505680</t>
+          <t>587387</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>524511</t>
+          <t>606770</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>508805</t>
+          <t>582524</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>498146</t>
+          <t>571657</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>517279</t>
+          <t>592140</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>91,89%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1024814</t>
+          <t>1181600</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1011646</t>
+          <t>1165365</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1037062</t>
+          <t>1194441</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,1%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>34308</t>
+          <t>37266</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14894</t>
+          <t>25768</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>54214</t>
+          <t>51012</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>68160</t>
+          <t>70716</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>52711</t>
+          <t>58889</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>87146</t>
+          <t>85520</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>102468</t>
+          <t>107982</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>60885</t>
+          <t>89071</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>131284</t>
+          <t>127646</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,88%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>853478</t>
+          <t>663351</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>833572</t>
+          <t>649605</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>872892</t>
+          <t>674849</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>644338</t>
+          <t>665779</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>625352</t>
+          <t>650975</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>659787</t>
+          <t>677606</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>90,4%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1497817</t>
+          <t>1329130</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1469001</t>
+          <t>1309466</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1539400</t>
+          <t>1348041</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>91,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>93,8%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>712498</t>
+          <t>736495</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>712498</t>
+          <t>736495</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>712498</t>
+          <t>736495</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1600285</t>
+          <t>1437112</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1600285</t>
+          <t>1437112</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1600285</t>
+          <t>1437112</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>54825</t>
+          <t>57581</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>43374</t>
+          <t>44959</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>69076</t>
+          <t>72841</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>106370</t>
+          <t>121041</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>91810</t>
+          <t>108100</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>120634</t>
+          <t>137794</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>161196</t>
+          <t>178621</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>141777</t>
+          <t>158070</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>179078</t>
+          <t>200700</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,51%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>504382</t>
+          <t>549696</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>490131</t>
+          <t>534436</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>515833</t>
+          <t>562318</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>90,52%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,65%</t>
+          <t>88,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>439196</t>
+          <t>487092</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>424932</t>
+          <t>470339</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>453756</t>
+          <t>500033</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>80,5%</t>
+          <t>80,1%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,89%</t>
+          <t>77,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,17%</t>
+          <t>82,22%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>943577</t>
+          <t>1036789</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>925695</t>
+          <t>1014710</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>962996</t>
+          <t>1057340</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>85,41%</t>
+          <t>85,3%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>83,79%</t>
+          <t>83,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,17%</t>
+          <t>86,99%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>559207</t>
+          <t>607277</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>559207</t>
+          <t>607277</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>559207</t>
+          <t>607277</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>545566</t>
+          <t>608133</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>545566</t>
+          <t>608133</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>545566</t>
+          <t>608133</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1104773</t>
+          <t>1215410</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1104773</t>
+          <t>1215410</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1104773</t>
+          <t>1215410</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2440,32 +2440,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>44329</t>
+          <t>48748</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>35200</t>
+          <t>38863</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>55451</t>
+          <t>59826</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>77600</t>
+          <t>85460</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>32476</t>
+          <t>72832</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>121293</t>
+          <t>96900</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>121929</t>
+          <t>134208</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>58434</t>
+          <t>118955</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>160068</t>
+          <t>151206</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>17,88%</t>
         </is>
       </c>
     </row>
@@ -2553,32 +2553,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>323836</t>
+          <t>358332</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>312714</t>
+          <t>347254</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>332965</t>
+          <t>368217</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>87,96%</t>
+          <t>88,02%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>84,94%</t>
+          <t>85,3%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>90,45%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>530178</t>
+          <t>353037</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>486485</t>
+          <t>341597</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>575302</t>
+          <t>365665</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>80,51%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>80,04%</t>
+          <t>77,9%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>83,39%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>854014</t>
+          <t>711369</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>815875</t>
+          <t>694371</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>917509</t>
+          <t>726622</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>87,51%</t>
+          <t>84,13%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>82,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>85,93%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>607778</t>
+          <t>438497</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>607778</t>
+          <t>438497</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>607778</t>
+          <t>438497</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>975943</t>
+          <t>845577</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>975943</t>
+          <t>845577</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>975943</t>
+          <t>845577</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>53893</t>
+          <t>59882</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>44046</t>
+          <t>48986</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>64650</t>
+          <t>72501</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>117743</t>
+          <t>130175</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>105189</t>
+          <t>116232</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>130457</t>
+          <t>145085</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>31,27%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>171636</t>
+          <t>190057</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>156382</t>
+          <t>171253</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>190901</t>
+          <t>209272</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>27,03%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>228866</t>
+          <t>250316</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>218109</t>
+          <t>237697</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>238713</t>
+          <t>261212</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>80,94%</t>
+          <t>80,7%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>77,14%</t>
+          <t>76,63%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>84,42%</t>
+          <t>84,21%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>307522</t>
+          <t>333838</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>294808</t>
+          <t>318928</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>320076</t>
+          <t>347781</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>72,31%</t>
+          <t>71,95%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>69,32%</t>
+          <t>68,73%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>75,26%</t>
+          <t>74,95%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>536388</t>
+          <t>584154</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>517123</t>
+          <t>564939</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>551642</t>
+          <t>602958</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>75,76%</t>
+          <t>75,45%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>73,04%</t>
+          <t>72,97%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>77,91%</t>
+          <t>77,88%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>425265</t>
+          <t>464013</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>425265</t>
+          <t>464013</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>425265</t>
+          <t>464013</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>708024</t>
+          <t>774211</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>708024</t>
+          <t>774211</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>708024</t>
+          <t>774211</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3126,32 +3126,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>218916</t>
+          <t>237576</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>168381</t>
+          <t>208439</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>253439</t>
+          <t>268293</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,32 +3161,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>427630</t>
+          <t>474236</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>348865</t>
+          <t>441591</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>472318</t>
+          <t>507802</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>646547</t>
+          <t>711812</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>557091</t>
+          <t>668340</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>705134</t>
+          <t>756581</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>10,42%</t>
         </is>
       </c>
     </row>
@@ -3239,32 +3239,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3238875</t>
+          <t>3293117</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3204352</t>
+          <t>3262400</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3289410</t>
+          <t>3322254</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,32 +3274,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3230649</t>
+          <t>3258637</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3185961</t>
+          <t>3225071</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3309414</t>
+          <t>3291282</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>87,3%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>87,09%</t>
+          <t>86,4%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>88,17%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>6469523</t>
+          <t>6551753</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6410936</t>
+          <t>6506984</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6558979</t>
+          <t>6595225</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>90,2%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>89,58%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>90,8%</t>
         </is>
       </c>
     </row>
@@ -3352,17 +3352,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3457791</t>
+          <t>3530693</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3457791</t>
+          <t>3530693</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3457791</t>
+          <t>3530693</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3658279</t>
+          <t>3732873</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3658279</t>
+          <t>3732873</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3658279</t>
+          <t>3732873</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7116070</t>
+          <t>7263565</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7116070</t>
+          <t>7263565</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7116070</t>
+          <t>7263565</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
